--- a/appData/upload_sample_manual_properly_formatted_excel.xlsx
+++ b/appData/upload_sample_manual_properly_formatted_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ianhe\OneDrive\Documents\Github\gamma_sandbox\appData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{336B608A-3BB3-4BF9-AB35-1AE745239831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0786E2-0848-47C6-894C-BC849F7D48A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="19200" windowHeight="11170" xr2:uid="{4B7F7DEF-D1CD-41F6-80DC-E580B7DB3B6E}"/>
+    <workbookView xWindow="8620" yWindow="3440" windowWidth="28800" windowHeight="15370" xr2:uid="{4B7F7DEF-D1CD-41F6-80DC-E580B7DB3B6E}"/>
   </bookViews>
   <sheets>
     <sheet name="upload_sample_manual_properly_f" sheetId="1" r:id="rId1"/>
@@ -23,9 +23,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="38">
   <si>
     <t>Accession Number</t>
-  </si>
-  <si>
-    <t>Taxon Name</t>
   </si>
   <si>
     <t>Current Germplasm Type</t>
@@ -134,6 +131,9 @@
   </si>
   <si>
     <t>Aaron Liston</t>
+  </si>
+  <si>
+    <t>Taxon Name</t>
   </si>
 </sst>
 </file>
@@ -996,34 +996,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D165D7-F585-4D69-ADD0-7349F7E15D66}">
   <dimension ref="A1:I201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -1031,13 +1042,13 @@
         <v>574</v>
       </c>
       <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>41.208300000000001</v>
@@ -1046,13 +1057,13 @@
         <v>-120.1767</v>
       </c>
       <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -1060,13 +1071,13 @@
         <v>574730172</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>41.208300000000001</v>
@@ -1075,13 +1086,13 @@
         <v>-120.1767</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" t="s">
         <v>13</v>
-      </c>
-      <c r="I3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -1089,13 +1100,13 @@
         <v>574751035</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>41.208300000000001</v>
@@ -1104,13 +1115,13 @@
         <v>-120.1767</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="s">
         <v>13</v>
-      </c>
-      <c r="I4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -1118,13 +1129,13 @@
         <v>574753591</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>49.033299999999997</v>
@@ -1133,13 +1144,13 @@
         <v>-118.08329999999999</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -1147,13 +1158,13 @@
         <v>574774665</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>41.208300000000001</v>
@@ -1162,13 +1173,13 @@
         <v>-120.1767</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" t="s">
         <v>13</v>
-      </c>
-      <c r="I6" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -1176,10 +1187,10 @@
         <v>5006902297</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>2025</v>
@@ -1191,13 +1202,13 @@
         <v>-122.2255</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -1205,10 +1216,10 @@
         <v>5063293749</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>2025</v>
@@ -1220,13 +1231,13 @@
         <v>-122.3638</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -1234,10 +1245,10 @@
         <v>5063561100</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9">
         <v>2025</v>
@@ -1249,13 +1260,13 @@
         <v>-116.2086</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -1263,10 +1274,10 @@
         <v>5063612592</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10">
         <v>2025</v>
@@ -1278,13 +1289,13 @@
         <v>-122.98009999999999</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -1292,10 +1303,10 @@
         <v>5069779155</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11">
         <v>2025</v>
@@ -1307,13 +1318,13 @@
         <v>-121.8768</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1321,10 +1332,10 @@
         <v>5063831752</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <v>2025</v>
@@ -1336,13 +1347,13 @@
         <v>-123.0136</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1350,10 +1361,10 @@
         <v>5076853759</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13">
         <v>2025</v>
@@ -1365,13 +1376,13 @@
         <v>-122.13800000000001</v>
       </c>
       <c r="G13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1379,10 +1390,10 @@
         <v>5076943122</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14">
         <v>2025</v>
@@ -1394,13 +1405,13 @@
         <v>-122.05800000000001</v>
       </c>
       <c r="G14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1408,10 +1419,10 @@
         <v>5077158576</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15">
         <v>2025</v>
@@ -1423,13 +1434,13 @@
         <v>-122.7911</v>
       </c>
       <c r="G15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1437,10 +1448,10 @@
         <v>5133778593</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16">
         <v>2025</v>
@@ -1452,13 +1463,13 @@
         <v>-117.2238</v>
       </c>
       <c r="G16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1466,10 +1477,10 @@
         <v>5087796425</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17">
         <v>2025</v>
@@ -1481,13 +1492,13 @@
         <v>-121.2206</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1495,10 +1506,10 @@
         <v>5133236955</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D18">
         <v>2025</v>
@@ -1510,13 +1521,13 @@
         <v>-122.9092</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H18" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" t="s">
         <v>30</v>
-      </c>
-      <c r="I18" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1524,10 +1535,10 @@
         <v>5133988061</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19">
         <v>2025</v>
@@ -1539,13 +1550,13 @@
         <v>-117.76730000000001</v>
       </c>
       <c r="G19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -1553,10 +1564,10 @@
         <v>5134446403</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20">
         <v>2025</v>
@@ -1568,13 +1579,13 @@
         <v>-123.2847</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1582,10 +1593,10 @@
         <v>5140752902</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21">
         <v>2025</v>
@@ -1597,13 +1608,13 @@
         <v>-122.95010000000001</v>
       </c>
       <c r="G21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -1611,10 +1622,10 @@
         <v>5154694428</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22">
         <v>2025</v>
@@ -1626,13 +1637,13 @@
         <v>-123.1566</v>
       </c>
       <c r="G22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -1640,10 +1651,10 @@
         <v>5198286129</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D23">
         <v>2025</v>
@@ -1655,13 +1666,13 @@
         <v>-117.75539999999999</v>
       </c>
       <c r="G23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1669,10 +1680,10 @@
         <v>5198743142</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D24">
         <v>2025</v>
@@ -1684,13 +1695,13 @@
         <v>-117.75700000000001</v>
       </c>
       <c r="G24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1698,10 +1709,10 @@
         <v>5198998126</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25">
         <v>2025</v>
@@ -1713,13 +1724,13 @@
         <v>-117.75190000000001</v>
       </c>
       <c r="G25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1727,10 +1738,10 @@
         <v>5199079154</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26">
         <v>2025</v>
@@ -1742,13 +1753,13 @@
         <v>-117.7559</v>
       </c>
       <c r="G26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1756,10 +1767,10 @@
         <v>5231051610</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D27">
         <v>2025</v>
@@ -1771,13 +1782,13 @@
         <v>-117.74120000000001</v>
       </c>
       <c r="G27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1785,10 +1796,10 @@
         <v>5230028756</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D28">
         <v>2025</v>
@@ -1800,13 +1811,13 @@
         <v>-117.19970000000001</v>
       </c>
       <c r="G28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1814,10 +1825,10 @@
         <v>5761179221</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D29">
         <v>2025</v>
@@ -1829,13 +1840,13 @@
         <v>-120.0972</v>
       </c>
       <c r="G29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -1843,10 +1854,10 @@
         <v>5205997782</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D30">
         <v>2025</v>
@@ -1858,13 +1869,13 @@
         <v>-116.7989</v>
       </c>
       <c r="G30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -1872,10 +1883,10 @@
         <v>5206087823</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D31">
         <v>2025</v>
@@ -1887,13 +1898,13 @@
         <v>-116.8092</v>
       </c>
       <c r="G31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -1901,10 +1912,10 @@
         <v>5206203791</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D32">
         <v>2025</v>
@@ -1916,13 +1927,13 @@
         <v>-116.7808</v>
       </c>
       <c r="G32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -1930,10 +1941,10 @@
         <v>5206235765</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D33">
         <v>2025</v>
@@ -1945,13 +1956,13 @@
         <v>-116.80589999999999</v>
       </c>
       <c r="G33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -1959,10 +1970,10 @@
         <v>5206299808</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D34">
         <v>2025</v>
@@ -1974,13 +1985,13 @@
         <v>-116.8085</v>
       </c>
       <c r="G34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -1988,10 +1999,10 @@
         <v>5206340778</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D35">
         <v>2025</v>
@@ -2003,13 +2014,13 @@
         <v>-116.8073</v>
       </c>
       <c r="G35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
@@ -2017,10 +2028,10 @@
         <v>5206507785</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D36">
         <v>2025</v>
@@ -2032,13 +2043,13 @@
         <v>-116.7976</v>
       </c>
       <c r="G36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -2046,10 +2057,10 @@
         <v>5206524773</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D37">
         <v>2025</v>
@@ -2061,13 +2072,13 @@
         <v>-116.80029999999999</v>
       </c>
       <c r="G37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -2075,10 +2086,10 @@
         <v>5206701770</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D38">
         <v>2025</v>
@@ -2090,13 +2101,13 @@
         <v>-116.79559999999999</v>
       </c>
       <c r="G38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
@@ -2104,10 +2115,10 @@
         <v>5206811776</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D39">
         <v>2025</v>
@@ -2119,13 +2130,13 @@
         <v>-116.7966</v>
       </c>
       <c r="G39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -2133,10 +2144,10 @@
         <v>5217068971</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D40">
         <v>2025</v>
@@ -2148,13 +2159,13 @@
         <v>-121.1347</v>
       </c>
       <c r="G40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -2162,10 +2173,10 @@
         <v>5229947810</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D41">
         <v>2025</v>
@@ -2177,13 +2188,13 @@
         <v>-117.032</v>
       </c>
       <c r="G41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -2191,10 +2202,10 @@
         <v>5229947811</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D42">
         <v>2025</v>
@@ -2206,13 +2217,13 @@
         <v>-116.7534</v>
       </c>
       <c r="G42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -2220,10 +2231,10 @@
         <v>5229948807</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D43">
         <v>2025</v>
@@ -2235,13 +2246,13 @@
         <v>-116.7924</v>
       </c>
       <c r="G43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
@@ -2249,10 +2260,10 @@
         <v>5229955820</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D44">
         <v>2025</v>
@@ -2264,13 +2275,13 @@
         <v>-116.7818</v>
       </c>
       <c r="G44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
@@ -2278,10 +2289,10 @@
         <v>5229966823</v>
       </c>
       <c r="B45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D45">
         <v>2025</v>
@@ -2293,13 +2304,13 @@
         <v>-116.983</v>
       </c>
       <c r="G45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
@@ -2307,10 +2318,10 @@
         <v>5229977863</v>
       </c>
       <c r="B46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D46">
         <v>2025</v>
@@ -2322,13 +2333,13 @@
         <v>-116.78440000000001</v>
       </c>
       <c r="G46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
@@ -2336,10 +2347,10 @@
         <v>5229981819</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D47">
         <v>2025</v>
@@ -2351,13 +2362,13 @@
         <v>-116.78400000000001</v>
       </c>
       <c r="G47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -2365,10 +2376,10 @@
         <v>5229983844</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D48">
         <v>2025</v>
@@ -2380,13 +2391,13 @@
         <v>-117.0339</v>
       </c>
       <c r="G48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
@@ -2394,10 +2405,10 @@
         <v>5229991824</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D49">
         <v>2025</v>
@@ -2409,13 +2420,13 @@
         <v>-116.7795</v>
       </c>
       <c r="G49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
@@ -2423,10 +2434,10 @@
         <v>5229999796</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D50">
         <v>2025</v>
@@ -2438,13 +2449,13 @@
         <v>-116.7868</v>
       </c>
       <c r="G50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -2452,10 +2463,10 @@
         <v>5230006797</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D51">
         <v>2025</v>
@@ -2467,13 +2478,13 @@
         <v>-116.8575</v>
       </c>
       <c r="G51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -2481,10 +2492,10 @@
         <v>5230014802</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D52">
         <v>2025</v>
@@ -2496,13 +2507,13 @@
         <v>-117.02119999999999</v>
       </c>
       <c r="G52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
@@ -2510,10 +2521,10 @@
         <v>5230182875</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D53">
         <v>2025</v>
@@ -2525,13 +2536,13 @@
         <v>-117.09</v>
       </c>
       <c r="G53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H53" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
@@ -2539,10 +2550,10 @@
         <v>5230185806</v>
       </c>
       <c r="B54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D54">
         <v>2025</v>
@@ -2554,13 +2565,13 @@
         <v>-116.77889999999999</v>
       </c>
       <c r="G54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
@@ -2568,10 +2579,10 @@
         <v>5230204837</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D55">
         <v>2025</v>
@@ -2583,13 +2594,13 @@
         <v>-116.7919</v>
       </c>
       <c r="G55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
@@ -2597,10 +2608,10 @@
         <v>5230212821</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D56">
         <v>2025</v>
@@ -2612,13 +2623,13 @@
         <v>-116.776</v>
       </c>
       <c r="G56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
@@ -2626,10 +2637,10 @@
         <v>5230252834</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D57">
         <v>2025</v>
@@ -2641,13 +2652,13 @@
         <v>-116.8597</v>
       </c>
       <c r="G57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -2655,10 +2666,10 @@
         <v>5230255794</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D58">
         <v>2025</v>
@@ -2670,13 +2681,13 @@
         <v>-116.77930000000001</v>
       </c>
       <c r="G58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -2684,10 +2695,10 @@
         <v>5230256819</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D59">
         <v>2025</v>
@@ -2699,13 +2710,13 @@
         <v>-116.861</v>
       </c>
       <c r="G59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
@@ -2713,10 +2724,10 @@
         <v>5230258824</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D60">
         <v>2025</v>
@@ -2728,13 +2739,13 @@
         <v>-116.7379</v>
       </c>
       <c r="G60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
@@ -2742,10 +2753,10 @@
         <v>5230276861</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D61">
         <v>2025</v>
@@ -2757,13 +2768,13 @@
         <v>-116.854</v>
       </c>
       <c r="G61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
@@ -2771,10 +2782,10 @@
         <v>5230311860</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D62">
         <v>2025</v>
@@ -2786,13 +2797,13 @@
         <v>-117.0103</v>
       </c>
       <c r="G62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
@@ -2800,10 +2811,10 @@
         <v>5230318879</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D63">
         <v>2025</v>
@@ -2815,13 +2826,13 @@
         <v>-116.7996</v>
       </c>
       <c r="G63" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
@@ -2829,10 +2840,10 @@
         <v>5230376821</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D64">
         <v>2025</v>
@@ -2844,13 +2855,13 @@
         <v>-117.07859999999999</v>
       </c>
       <c r="G64" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
@@ -2858,10 +2869,10 @@
         <v>5230379806</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D65">
         <v>2025</v>
@@ -2873,13 +2884,13 @@
         <v>-116.84650000000001</v>
       </c>
       <c r="G65" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H65" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
@@ -2887,10 +2898,10 @@
         <v>5230387822</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D66">
         <v>2025</v>
@@ -2902,13 +2913,13 @@
         <v>-116.7976</v>
       </c>
       <c r="G66" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
@@ -2916,10 +2927,10 @@
         <v>5230395846</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D67">
         <v>2025</v>
@@ -2931,13 +2942,13 @@
         <v>-117.0547</v>
       </c>
       <c r="G67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
@@ -2945,10 +2956,10 @@
         <v>5230395847</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D68">
         <v>2025</v>
@@ -2960,13 +2971,13 @@
         <v>-116.9783</v>
       </c>
       <c r="G68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
@@ -2974,10 +2985,10 @@
         <v>5230416841</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D69">
         <v>2025</v>
@@ -2989,13 +3000,13 @@
         <v>-116.7972</v>
       </c>
       <c r="G69" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
@@ -3003,10 +3014,10 @@
         <v>5230420822</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D70">
         <v>2025</v>
@@ -3018,13 +3029,13 @@
         <v>-116.8592</v>
       </c>
       <c r="G70" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
@@ -3032,10 +3043,10 @@
         <v>5230421820</v>
       </c>
       <c r="B71" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D71">
         <v>2025</v>
@@ -3047,13 +3058,13 @@
         <v>-116.80119999999999</v>
       </c>
       <c r="G71" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I71" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
@@ -3061,10 +3072,10 @@
         <v>5230430812</v>
       </c>
       <c r="B72" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D72">
         <v>2025</v>
@@ -3076,13 +3087,13 @@
         <v>-117.0766</v>
       </c>
       <c r="G72" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I72" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
@@ -3090,10 +3101,10 @@
         <v>5230449823</v>
       </c>
       <c r="B73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D73">
         <v>2025</v>
@@ -3105,13 +3116,13 @@
         <v>-117.0266</v>
       </c>
       <c r="G73" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H73" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I73" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
@@ -3119,10 +3130,10 @@
         <v>5230455844</v>
       </c>
       <c r="B74" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D74">
         <v>2025</v>
@@ -3134,13 +3145,13 @@
         <v>-116.797</v>
       </c>
       <c r="G74" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H74" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
@@ -3148,10 +3159,10 @@
         <v>5230507818</v>
       </c>
       <c r="B75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D75">
         <v>2025</v>
@@ -3163,13 +3174,13 @@
         <v>-116.7769</v>
       </c>
       <c r="G75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
@@ -3177,10 +3188,10 @@
         <v>5230511824</v>
       </c>
       <c r="B76" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D76">
         <v>2025</v>
@@ -3192,13 +3203,13 @@
         <v>-116.7754</v>
       </c>
       <c r="G76" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H76" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I76" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
@@ -3206,10 +3217,10 @@
         <v>5230527810</v>
       </c>
       <c r="B77" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D77">
         <v>2025</v>
@@ -3221,13 +3232,13 @@
         <v>-116.80159999999999</v>
       </c>
       <c r="G77" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
@@ -3235,10 +3246,10 @@
         <v>5230548847</v>
       </c>
       <c r="B78" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D78">
         <v>2025</v>
@@ -3250,13 +3261,13 @@
         <v>-116.8008</v>
       </c>
       <c r="G78" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H78" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
@@ -3264,10 +3275,10 @@
         <v>5230552830</v>
       </c>
       <c r="B79" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D79">
         <v>2025</v>
@@ -3279,13 +3290,13 @@
         <v>-116.8672</v>
       </c>
       <c r="G79" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
@@ -3293,10 +3304,10 @@
         <v>5230555805</v>
       </c>
       <c r="B80" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D80">
         <v>2025</v>
@@ -3308,13 +3319,13 @@
         <v>-116.8021</v>
       </c>
       <c r="G80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H80" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
@@ -3322,10 +3333,10 @@
         <v>5230556773</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D81">
         <v>2025</v>
@@ -3337,13 +3348,13 @@
         <v>-116.8104</v>
       </c>
       <c r="G81" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H81" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I81" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
@@ -3351,10 +3362,10 @@
         <v>5230696834</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D82">
         <v>2025</v>
@@ -3366,13 +3377,13 @@
         <v>-116.8603</v>
       </c>
       <c r="G82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H82" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I82" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
@@ -3380,10 +3391,10 @@
         <v>5230717850</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D83">
         <v>2025</v>
@@ -3395,13 +3406,13 @@
         <v>-117.0239</v>
       </c>
       <c r="G83" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H83" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I83" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
@@ -3409,10 +3420,10 @@
         <v>5230719817</v>
       </c>
       <c r="B84" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D84">
         <v>2025</v>
@@ -3424,13 +3435,13 @@
         <v>-116.7801</v>
       </c>
       <c r="G84" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H84" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
@@ -3438,10 +3449,10 @@
         <v>5230730850</v>
       </c>
       <c r="B85" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D85">
         <v>2025</v>
@@ -3453,13 +3464,13 @@
         <v>-116.77679999999999</v>
       </c>
       <c r="G85" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H85" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
@@ -3467,10 +3478,10 @@
         <v>5230770840</v>
       </c>
       <c r="B86" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D86">
         <v>2025</v>
@@ -3482,13 +3493,13 @@
         <v>-116.85120000000001</v>
       </c>
       <c r="G86" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H86" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
@@ -3496,10 +3507,10 @@
         <v>5230799847</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D87">
         <v>2025</v>
@@ -3511,13 +3522,13 @@
         <v>-116.9025</v>
       </c>
       <c r="G87" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H87" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I87" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
@@ -3525,10 +3536,10 @@
         <v>5230817807</v>
       </c>
       <c r="B88" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D88">
         <v>2025</v>
@@ -3540,13 +3551,13 @@
         <v>-116.9937</v>
       </c>
       <c r="G88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H88" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
@@ -3554,10 +3565,10 @@
         <v>5230836833</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D89">
         <v>2025</v>
@@ -3569,13 +3580,13 @@
         <v>-116.7923</v>
       </c>
       <c r="G89" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H89" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
@@ -3583,10 +3594,10 @@
         <v>5230844841</v>
       </c>
       <c r="B90" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D90">
         <v>2025</v>
@@ -3598,13 +3609,13 @@
         <v>-116.7749</v>
       </c>
       <c r="G90" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H90" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I90" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
@@ -3612,10 +3623,10 @@
         <v>5230851797</v>
       </c>
       <c r="B91" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D91">
         <v>2025</v>
@@ -3627,13 +3638,13 @@
         <v>-116.79730000000001</v>
       </c>
       <c r="G91" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H91" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I91" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
@@ -3641,10 +3652,10 @@
         <v>5230855912</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D92">
         <v>2025</v>
@@ -3656,13 +3667,13 @@
         <v>-117.0496</v>
       </c>
       <c r="G92" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H92" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I92" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
@@ -3670,10 +3681,10 @@
         <v>5230861812</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D93">
         <v>2025</v>
@@ -3685,13 +3696,13 @@
         <v>-116.8052</v>
       </c>
       <c r="G93" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H93" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I93" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
@@ -3699,10 +3710,10 @@
         <v>5230872850</v>
       </c>
       <c r="B94" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D94">
         <v>2025</v>
@@ -3714,13 +3725,13 @@
         <v>-116.7966</v>
       </c>
       <c r="G94" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H94" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I94" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
@@ -3728,10 +3739,10 @@
         <v>5230896805</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D95">
         <v>2025</v>
@@ -3743,13 +3754,13 @@
         <v>-116.9855</v>
       </c>
       <c r="G95" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H95" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I95" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
@@ -3757,10 +3768,10 @@
         <v>5230896807</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D96">
         <v>2025</v>
@@ -3772,13 +3783,13 @@
         <v>-116.8028</v>
       </c>
       <c r="G96" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H96" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I96" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
@@ -3786,10 +3797,10 @@
         <v>5230914812</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D97">
         <v>2025</v>
@@ -3801,13 +3812,13 @@
         <v>-116.76649999999999</v>
       </c>
       <c r="G97" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H97" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I97" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
@@ -3815,10 +3826,10 @@
         <v>5230929800</v>
       </c>
       <c r="B98" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D98">
         <v>2025</v>
@@ -3830,13 +3841,13 @@
         <v>-116.7779</v>
       </c>
       <c r="G98" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H98" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I98" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
@@ -3844,10 +3855,10 @@
         <v>5230930851</v>
       </c>
       <c r="B99" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D99">
         <v>2025</v>
@@ -3859,13 +3870,13 @@
         <v>-116.8597</v>
       </c>
       <c r="G99" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H99" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I99" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
@@ -3873,10 +3884,10 @@
         <v>5230977829</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D100">
         <v>2025</v>
@@ -3888,13 +3899,13 @@
         <v>-117.0314</v>
       </c>
       <c r="G100" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H100" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I100" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
@@ -3902,10 +3913,10 @@
         <v>5231019821</v>
       </c>
       <c r="B101" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D101">
         <v>2025</v>
@@ -3917,13 +3928,13 @@
         <v>-116.8648</v>
       </c>
       <c r="G101" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H101" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I101" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
@@ -3931,10 +3942,10 @@
         <v>5231031824</v>
       </c>
       <c r="B102" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D102">
         <v>2025</v>
@@ -3946,13 +3957,13 @@
         <v>-116.77760000000001</v>
       </c>
       <c r="G102" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H102" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I102" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
@@ -3960,10 +3971,10 @@
         <v>5231048785</v>
       </c>
       <c r="B103" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C103" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D103">
         <v>2025</v>
@@ -3975,13 +3986,13 @@
         <v>-117.0851</v>
       </c>
       <c r="G103" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H103" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I103" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
@@ -3989,10 +4000,10 @@
         <v>5231082818</v>
       </c>
       <c r="B104" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C104" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D104">
         <v>2025</v>
@@ -4004,13 +4015,13 @@
         <v>-116.76609999999999</v>
       </c>
       <c r="G104" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H104" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I104" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
@@ -4018,10 +4029,10 @@
         <v>5231087848</v>
       </c>
       <c r="B105" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D105">
         <v>2025</v>
@@ -4033,13 +4044,13 @@
         <v>-117.03360000000001</v>
       </c>
       <c r="G105" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H105" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I105" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.35">
@@ -4047,10 +4058,10 @@
         <v>5231116796</v>
       </c>
       <c r="B106" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C106" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D106">
         <v>2025</v>
@@ -4062,13 +4073,13 @@
         <v>-116.97929999999999</v>
       </c>
       <c r="G106" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H106" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I106" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.35">
@@ -4076,10 +4087,10 @@
         <v>5231132810</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C107" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D107">
         <v>2025</v>
@@ -4091,13 +4102,13 @@
         <v>-116.79089999999999</v>
       </c>
       <c r="G107" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H107" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
@@ -4105,10 +4116,10 @@
         <v>5231187813</v>
       </c>
       <c r="B108" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D108">
         <v>2025</v>
@@ -4120,13 +4131,13 @@
         <v>-116.845</v>
       </c>
       <c r="G108" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H108" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I108" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
@@ -4134,10 +4145,10 @@
         <v>5231238806</v>
       </c>
       <c r="B109" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D109">
         <v>2025</v>
@@ -4149,13 +4160,13 @@
         <v>-116.7816</v>
       </c>
       <c r="G109" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H109" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I109" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.35">
@@ -4163,10 +4174,10 @@
         <v>5231245822</v>
       </c>
       <c r="B110" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C110" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D110">
         <v>2025</v>
@@ -4178,13 +4189,13 @@
         <v>-116.7807</v>
       </c>
       <c r="G110" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H110" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I110" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
@@ -4192,10 +4203,10 @@
         <v>5231256804</v>
       </c>
       <c r="B111" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C111" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D111">
         <v>2025</v>
@@ -4207,13 +4218,13 @@
         <v>-116.8133</v>
       </c>
       <c r="G111" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H111" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I111" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
@@ -4221,10 +4232,10 @@
         <v>5231298804</v>
       </c>
       <c r="B112" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C112" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D112">
         <v>2025</v>
@@ -4236,13 +4247,13 @@
         <v>-116.7809</v>
       </c>
       <c r="G112" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H112" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I112" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.35">
@@ -4250,10 +4261,10 @@
         <v>5231303855</v>
       </c>
       <c r="B113" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D113">
         <v>2025</v>
@@ -4265,13 +4276,13 @@
         <v>-116.79179999999999</v>
       </c>
       <c r="G113" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H113" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I113" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.35">
@@ -4279,10 +4290,10 @@
         <v>5231357836</v>
       </c>
       <c r="B114" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C114" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D114">
         <v>2025</v>
@@ -4294,13 +4305,13 @@
         <v>-116.79300000000001</v>
       </c>
       <c r="G114" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H114" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I114" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.35">
@@ -4308,10 +4319,10 @@
         <v>5231389811</v>
       </c>
       <c r="B115" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C115" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D115">
         <v>2025</v>
@@ -4323,13 +4334,13 @@
         <v>-116.9113</v>
       </c>
       <c r="G115" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I115" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.35">
@@ -4337,10 +4348,10 @@
         <v>5231399833</v>
       </c>
       <c r="B116" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C116" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D116">
         <v>2025</v>
@@ -4352,13 +4363,13 @@
         <v>-116.8168</v>
       </c>
       <c r="G116" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I116" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.35">
@@ -4366,10 +4377,10 @@
         <v>5231414801</v>
       </c>
       <c r="B117" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C117" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D117">
         <v>2025</v>
@@ -4381,13 +4392,13 @@
         <v>-116.9064</v>
       </c>
       <c r="G117" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I117" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
@@ -4395,10 +4406,10 @@
         <v>5231450822</v>
       </c>
       <c r="B118" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D118">
         <v>2025</v>
@@ -4410,13 +4421,13 @@
         <v>-116.812</v>
       </c>
       <c r="G118" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H118" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I118" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.35">
@@ -4424,10 +4435,10 @@
         <v>5231459797</v>
       </c>
       <c r="B119" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C119" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D119">
         <v>2025</v>
@@ -4439,13 +4450,13 @@
         <v>-116.79179999999999</v>
       </c>
       <c r="G119" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H119" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I119" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.35">
@@ -4453,10 +4464,10 @@
         <v>5231491840</v>
       </c>
       <c r="B120" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C120" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D120">
         <v>2025</v>
@@ -4468,13 +4479,13 @@
         <v>-116.8031</v>
       </c>
       <c r="G120" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I120" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.35">
@@ -4482,10 +4493,10 @@
         <v>5231517770</v>
       </c>
       <c r="B121" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C121" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D121">
         <v>2025</v>
@@ -4497,13 +4508,13 @@
         <v>-116.73990000000001</v>
       </c>
       <c r="G121" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I121" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
@@ -4511,10 +4522,10 @@
         <v>5231521836</v>
       </c>
       <c r="B122" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C122" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D122">
         <v>2025</v>
@@ -4526,13 +4537,13 @@
         <v>-116.9877</v>
       </c>
       <c r="G122" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H122" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I122" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
@@ -4540,10 +4551,10 @@
         <v>5231550770</v>
       </c>
       <c r="B123" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D123">
         <v>2025</v>
@@ -4555,13 +4566,13 @@
         <v>-116.7807</v>
       </c>
       <c r="G123" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H123" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I123" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
@@ -4569,10 +4580,10 @@
         <v>5231586828</v>
       </c>
       <c r="B124" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C124" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D124">
         <v>2025</v>
@@ -4584,13 +4595,13 @@
         <v>-116.7786</v>
       </c>
       <c r="G124" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H124" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I124" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.35">
@@ -4598,10 +4609,10 @@
         <v>5215783278</v>
       </c>
       <c r="B125" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C125" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D125">
         <v>2025</v>
@@ -4613,13 +4624,13 @@
         <v>-119.2749</v>
       </c>
       <c r="G125" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H125" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I125" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.35">
@@ -4627,10 +4638,10 @@
         <v>5215814258</v>
       </c>
       <c r="B126" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C126" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D126">
         <v>2025</v>
@@ -4642,13 +4653,13 @@
         <v>-119.28019999999999</v>
       </c>
       <c r="G126" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H126" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I126" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.35">
@@ -4656,10 +4667,10 @@
         <v>5216128306</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C127" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D127">
         <v>2025</v>
@@ -4671,13 +4682,13 @@
         <v>-119.2787</v>
       </c>
       <c r="G127" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H127" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I127" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.35">
@@ -4685,10 +4696,10 @@
         <v>5216133379</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C128" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D128">
         <v>2025</v>
@@ -4700,13 +4711,13 @@
         <v>-119.3109</v>
       </c>
       <c r="G128" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H128" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I128" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.35">
@@ -4714,10 +4725,10 @@
         <v>5216796316</v>
       </c>
       <c r="B129" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D129">
         <v>2025</v>
@@ -4729,13 +4740,13 @@
         <v>-119.2774</v>
       </c>
       <c r="G129" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H129" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I129" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.35">
@@ -4743,10 +4754,10 @@
         <v>5216996383</v>
       </c>
       <c r="B130" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D130">
         <v>2025</v>
@@ -4758,13 +4769,13 @@
         <v>-119.3103</v>
       </c>
       <c r="G130" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I130" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.35">
@@ -4772,10 +4783,10 @@
         <v>5217112348</v>
       </c>
       <c r="B131" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C131" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D131">
         <v>2025</v>
@@ -4787,13 +4798,13 @@
         <v>-119.2784</v>
       </c>
       <c r="G131" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H131" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I131" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.35">
@@ -4801,10 +4812,10 @@
         <v>5217446375</v>
       </c>
       <c r="B132" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C132" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D132">
         <v>2025</v>
@@ -4816,13 +4827,13 @@
         <v>-119.2745</v>
       </c>
       <c r="G132" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H132" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I132" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.35">
@@ -4830,10 +4841,10 @@
         <v>5217515315</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C133" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D133">
         <v>2025</v>
@@ -4845,13 +4856,13 @@
         <v>-119.2796</v>
       </c>
       <c r="G133" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H133" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I133" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.35">
@@ -4859,10 +4870,10 @@
         <v>5230044048</v>
       </c>
       <c r="B134" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C134" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D134">
         <v>2025</v>
@@ -4874,13 +4885,13 @@
         <v>-117.27970000000001</v>
       </c>
       <c r="G134" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H134" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I134" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.35">
@@ -4888,10 +4899,10 @@
         <v>5230051198</v>
       </c>
       <c r="B135" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C135" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D135">
         <v>2025</v>
@@ -4903,13 +4914,13 @@
         <v>-118.5483</v>
       </c>
       <c r="G135" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H135" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I135" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.35">
@@ -4917,10 +4928,10 @@
         <v>5230060085</v>
       </c>
       <c r="B136" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C136" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D136">
         <v>2025</v>
@@ -4932,13 +4943,13 @@
         <v>-117.2749</v>
       </c>
       <c r="G136" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H136" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I136" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.35">
@@ -4946,10 +4957,10 @@
         <v>5230061029</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C137" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D137">
         <v>2025</v>
@@ -4961,13 +4972,13 @@
         <v>-117.2405</v>
       </c>
       <c r="G137" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H137" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I137" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.35">
@@ -4975,10 +4986,10 @@
         <v>5230072041</v>
       </c>
       <c r="B138" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D138">
         <v>2025</v>
@@ -4990,13 +5001,13 @@
         <v>-117.2959</v>
       </c>
       <c r="G138" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H138" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I138" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.35">
@@ -5004,10 +5015,10 @@
         <v>5230084083</v>
       </c>
       <c r="B139" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C139" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D139">
         <v>2025</v>
@@ -5019,13 +5030,13 @@
         <v>-117.2677</v>
       </c>
       <c r="G139" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H139" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I139" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.35">
@@ -5033,10 +5044,10 @@
         <v>5230146348</v>
       </c>
       <c r="B140" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C140" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D140">
         <v>2025</v>
@@ -5048,13 +5059,13 @@
         <v>-118.6627</v>
       </c>
       <c r="G140" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H140" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I140" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.35">
@@ -5062,10 +5073,10 @@
         <v>5230168386</v>
       </c>
       <c r="B141" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C141" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D141">
         <v>2025</v>
@@ -5077,13 +5088,13 @@
         <v>-118.8669</v>
       </c>
       <c r="G141" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H141" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I141" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.35">
@@ -5091,10 +5102,10 @@
         <v>5230218301</v>
       </c>
       <c r="B142" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C142" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D142">
         <v>2025</v>
@@ -5106,13 +5117,13 @@
         <v>-118.74039999999999</v>
       </c>
       <c r="G142" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H142" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I142" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.35">
@@ -5120,10 +5131,10 @@
         <v>5230233397</v>
       </c>
       <c r="B143" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D143">
         <v>2025</v>
@@ -5135,13 +5146,13 @@
         <v>-119.01990000000001</v>
       </c>
       <c r="G143" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H143" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I143" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.35">
@@ -5149,10 +5160,10 @@
         <v>5230248317</v>
       </c>
       <c r="B144" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D144">
         <v>2025</v>
@@ -5164,13 +5175,13 @@
         <v>-118.587</v>
       </c>
       <c r="G144" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H144" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I144" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.35">
@@ -5178,10 +5189,10 @@
         <v>5230268319</v>
       </c>
       <c r="B145" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D145">
         <v>2025</v>
@@ -5193,13 +5204,13 @@
         <v>-119.006</v>
       </c>
       <c r="G145" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H145" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I145" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.35">
@@ -5207,10 +5218,10 @@
         <v>5230328062</v>
       </c>
       <c r="B146" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C146" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D146">
         <v>2025</v>
@@ -5222,13 +5233,13 @@
         <v>-117.2831</v>
       </c>
       <c r="G146" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H146" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I146" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.35">
@@ -5236,10 +5247,10 @@
         <v>5230364065</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D147">
         <v>2025</v>
@@ -5251,13 +5262,13 @@
         <v>-117.2766</v>
       </c>
       <c r="G147" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H147" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I147" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.35">
@@ -5265,10 +5276,10 @@
         <v>5230379039</v>
       </c>
       <c r="B148" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D148">
         <v>2025</v>
@@ -5280,13 +5291,13 @@
         <v>-117.292</v>
       </c>
       <c r="G148" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H148" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I148" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.35">
@@ -5294,10 +5305,10 @@
         <v>5230412025</v>
       </c>
       <c r="B149" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D149">
         <v>2025</v>
@@ -5309,13 +5320,13 @@
         <v>-117.2632</v>
       </c>
       <c r="G149" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H149" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I149" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.35">
@@ -5323,10 +5334,10 @@
         <v>5230412280</v>
       </c>
       <c r="B150" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D150">
         <v>2025</v>
@@ -5338,13 +5349,13 @@
         <v>-119.0384</v>
       </c>
       <c r="G150" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H150" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I150" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.35">
@@ -5352,10 +5363,10 @@
         <v>5230437057</v>
       </c>
       <c r="B151" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D151">
         <v>2025</v>
@@ -5367,13 +5378,13 @@
         <v>-118.199</v>
       </c>
       <c r="G151" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H151" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I151" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.35">
@@ -5381,10 +5392,10 @@
         <v>5230441277</v>
       </c>
       <c r="B152" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D152">
         <v>2025</v>
@@ -5396,13 +5407,13 @@
         <v>-118.71850000000001</v>
       </c>
       <c r="G152" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H152" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I152" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.35">
@@ -5410,10 +5421,10 @@
         <v>5230476042</v>
       </c>
       <c r="B153" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D153">
         <v>2025</v>
@@ -5425,13 +5436,13 @@
         <v>-117.2824</v>
       </c>
       <c r="G153" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H153" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I153" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.35">
@@ -5439,10 +5450,10 @@
         <v>5230495309</v>
       </c>
       <c r="B154" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D154">
         <v>2025</v>
@@ -5454,13 +5465,13 @@
         <v>-118.50620000000001</v>
       </c>
       <c r="G154" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H154" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I154" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.35">
@@ -5468,10 +5479,10 @@
         <v>5230508336</v>
       </c>
       <c r="B155" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D155">
         <v>2025</v>
@@ -5483,13 +5494,13 @@
         <v>-118.8151</v>
       </c>
       <c r="G155" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H155" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I155" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.35">
@@ -5497,10 +5508,10 @@
         <v>5230529320</v>
       </c>
       <c r="B156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D156">
         <v>2025</v>
@@ -5512,13 +5523,13 @@
         <v>-118.83580000000001</v>
       </c>
       <c r="G156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H156" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I156" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.35">
@@ -5526,10 +5537,10 @@
         <v>5230560059</v>
       </c>
       <c r="B157" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D157">
         <v>2025</v>
@@ -5541,13 +5552,13 @@
         <v>-117.2714</v>
       </c>
       <c r="G157" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H157" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I157" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.35">
@@ -5555,10 +5566,10 @@
         <v>5230579049</v>
       </c>
       <c r="B158" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D158">
         <v>2025</v>
@@ -5570,13 +5581,13 @@
         <v>-117.2723</v>
       </c>
       <c r="G158" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H158" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I158" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.35">
@@ -5584,10 +5595,10 @@
         <v>5230583051</v>
       </c>
       <c r="B159" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D159">
         <v>2025</v>
@@ -5599,13 +5610,13 @@
         <v>-117.2732</v>
       </c>
       <c r="G159" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H159" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I159" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.35">
@@ -5613,10 +5624,10 @@
         <v>5230592035</v>
       </c>
       <c r="B160" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D160">
         <v>2025</v>
@@ -5628,13 +5639,13 @@
         <v>-117.2987</v>
       </c>
       <c r="G160" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H160" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I160" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.35">
@@ -5642,10 +5653,10 @@
         <v>5230592296</v>
       </c>
       <c r="B161" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D161">
         <v>2025</v>
@@ -5657,13 +5668,13 @@
         <v>-119.03319999999999</v>
       </c>
       <c r="G161" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H161" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I161" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.35">
@@ -5671,10 +5682,10 @@
         <v>5230606300</v>
       </c>
       <c r="B162" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D162">
         <v>2025</v>
@@ -5686,13 +5697,13 @@
         <v>-118.9692</v>
       </c>
       <c r="G162" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H162" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I162" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.35">
@@ -5700,10 +5711,10 @@
         <v>5230610339</v>
       </c>
       <c r="B163" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D163">
         <v>2025</v>
@@ -5715,13 +5726,13 @@
         <v>-119.0163</v>
       </c>
       <c r="G163" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H163" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I163" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.35">
@@ -5729,10 +5740,10 @@
         <v>5230625351</v>
       </c>
       <c r="B164" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D164">
         <v>2025</v>
@@ -5744,13 +5755,13 @@
         <v>-119.355</v>
       </c>
       <c r="G164" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H164" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I164" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.35">
@@ -5758,10 +5769,10 @@
         <v>5230625355</v>
       </c>
       <c r="B165" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D165">
         <v>2025</v>
@@ -5773,13 +5784,13 @@
         <v>-118.81019999999999</v>
       </c>
       <c r="G165" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H165" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I165" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.35">
@@ -5787,10 +5798,10 @@
         <v>5230628350</v>
       </c>
       <c r="B166" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D166">
         <v>2025</v>
@@ -5802,13 +5813,13 @@
         <v>-118.8708</v>
       </c>
       <c r="G166" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H166" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I166" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.35">
@@ -5816,10 +5827,10 @@
         <v>5230649381</v>
       </c>
       <c r="B167" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D167">
         <v>2025</v>
@@ -5831,13 +5842,13 @@
         <v>-118.8409</v>
       </c>
       <c r="G167" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H167" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I167" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.35">
@@ -5845,10 +5856,10 @@
         <v>5230662121</v>
       </c>
       <c r="B168" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D168">
         <v>2025</v>
@@ -5860,13 +5871,13 @@
         <v>-117.29519999999999</v>
       </c>
       <c r="G168" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H168" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I168" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.35">
@@ -5874,10 +5885,10 @@
         <v>5230695391</v>
       </c>
       <c r="B169" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D169">
         <v>2025</v>
@@ -5889,13 +5900,13 @@
         <v>-118.5539</v>
       </c>
       <c r="G169" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H169" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I169" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.35">
@@ -5903,10 +5914,10 @@
         <v>5230753358</v>
       </c>
       <c r="B170" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D170">
         <v>2025</v>
@@ -5918,13 +5929,13 @@
         <v>-118.9774</v>
       </c>
       <c r="G170" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H170" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I170" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.35">
@@ -5932,10 +5943,10 @@
         <v>5230766067</v>
       </c>
       <c r="B171" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C171" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D171">
         <v>2025</v>
@@ -5947,13 +5958,13 @@
         <v>-117.2864</v>
       </c>
       <c r="G171" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H171" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I171" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.35">
@@ -5961,10 +5972,10 @@
         <v>5230835270</v>
       </c>
       <c r="B172" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C172" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D172">
         <v>2025</v>
@@ -5976,13 +5987,13 @@
         <v>-118.9867</v>
       </c>
       <c r="G172" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H172" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I172" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.35">
@@ -5990,10 +6001,10 @@
         <v>5230884357</v>
       </c>
       <c r="B173" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C173" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D173">
         <v>2025</v>
@@ -6005,13 +6016,13 @@
         <v>-118.8837</v>
       </c>
       <c r="G173" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H173" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I173" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.35">
@@ -6019,10 +6030,10 @@
         <v>5230893305</v>
       </c>
       <c r="B174" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C174" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D174">
         <v>2025</v>
@@ -6034,13 +6045,13 @@
         <v>-118.8143</v>
       </c>
       <c r="G174" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H174" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I174" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.35">
@@ -6048,10 +6059,10 @@
         <v>5230908991</v>
       </c>
       <c r="B175" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C175" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D175">
         <v>2025</v>
@@ -6063,13 +6074,13 @@
         <v>-117.2791</v>
       </c>
       <c r="G175" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H175" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I175" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.35">
@@ -6077,10 +6088,10 @@
         <v>5230909242</v>
       </c>
       <c r="B176" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C176" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D176">
         <v>2025</v>
@@ -6092,13 +6103,13 @@
         <v>-118.8272</v>
       </c>
       <c r="G176" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H176" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I176" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.35">
@@ -6106,10 +6117,10 @@
         <v>5230971131</v>
       </c>
       <c r="B177" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C177" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D177">
         <v>2025</v>
@@ -6121,13 +6132,13 @@
         <v>-117.2846</v>
       </c>
       <c r="G177" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H177" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I177" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.35">
@@ -6135,10 +6146,10 @@
         <v>5231001215</v>
       </c>
       <c r="B178" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C178" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D178">
         <v>2025</v>
@@ -6150,13 +6161,13 @@
         <v>-118.8736</v>
       </c>
       <c r="G178" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H178" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I178" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.35">
@@ -6164,10 +6175,10 @@
         <v>5231008271</v>
       </c>
       <c r="B179" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C179" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D179">
         <v>2025</v>
@@ -6179,13 +6190,13 @@
         <v>-119.0299</v>
       </c>
       <c r="G179" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H179" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I179" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.35">
@@ -6193,10 +6204,10 @@
         <v>5231033040</v>
       </c>
       <c r="B180" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C180" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D180">
         <v>2025</v>
@@ -6208,13 +6219,13 @@
         <v>-118.1956</v>
       </c>
       <c r="G180" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H180" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I180" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.35">
@@ -6222,10 +6233,10 @@
         <v>5231040373</v>
       </c>
       <c r="B181" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C181" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D181">
         <v>2025</v>
@@ -6237,13 +6248,13 @@
         <v>-118.58969999999999</v>
       </c>
       <c r="G181" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H181" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I181" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.35">
@@ -6251,10 +6262,10 @@
         <v>5231058294</v>
       </c>
       <c r="B182" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C182" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D182">
         <v>2025</v>
@@ -6266,13 +6277,13 @@
         <v>-118.56270000000001</v>
       </c>
       <c r="G182" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H182" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I182" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.35">
@@ -6280,10 +6291,10 @@
         <v>5231060030</v>
       </c>
       <c r="B183" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C183" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D183">
         <v>2025</v>
@@ -6295,13 +6306,13 @@
         <v>-117.2927</v>
       </c>
       <c r="G183" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H183" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I183" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.35">
@@ -6309,10 +6320,10 @@
         <v>5231072000</v>
       </c>
       <c r="B184" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C184" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D184">
         <v>2025</v>
@@ -6324,13 +6335,13 @@
         <v>-117.27509999999999</v>
       </c>
       <c r="G184" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H184" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I184" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.35">
@@ -6338,10 +6349,10 @@
         <v>5231072237</v>
       </c>
       <c r="B185" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C185" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D185">
         <v>2025</v>
@@ -6353,13 +6364,13 @@
         <v>-118.57989999999999</v>
       </c>
       <c r="G185" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H185" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I185" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.35">
@@ -6367,10 +6378,10 @@
         <v>5231115084</v>
       </c>
       <c r="B186" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C186" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D186">
         <v>2025</v>
@@ -6382,13 +6393,13 @@
         <v>-117.2808</v>
       </c>
       <c r="G186" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H186" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I186" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.35">
@@ -6396,10 +6407,10 @@
         <v>5231120041</v>
       </c>
       <c r="B187" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C187" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D187">
         <v>2025</v>
@@ -6411,13 +6422,13 @@
         <v>-117.289</v>
       </c>
       <c r="G187" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H187" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I187" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.35">
@@ -6425,10 +6436,10 @@
         <v>5231154086</v>
       </c>
       <c r="B188" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C188" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D188">
         <v>2025</v>
@@ -6440,13 +6451,13 @@
         <v>-117.273</v>
       </c>
       <c r="G188" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H188" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I188" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.35">
@@ -6454,10 +6465,10 @@
         <v>5231158317</v>
       </c>
       <c r="B189" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C189" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D189">
         <v>2025</v>
@@ -6469,13 +6480,13 @@
         <v>-118.57210000000001</v>
       </c>
       <c r="G189" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H189" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I189" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.35">
@@ -6483,10 +6494,10 @@
         <v>5231196263</v>
       </c>
       <c r="B190" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C190" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D190">
         <v>2025</v>
@@ -6498,13 +6509,13 @@
         <v>-118.88039999999999</v>
       </c>
       <c r="G190" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H190" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I190" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.35">
@@ -6512,10 +6523,10 @@
         <v>5231230317</v>
       </c>
       <c r="B191" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C191" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D191">
         <v>2025</v>
@@ -6527,13 +6538,13 @@
         <v>-118.8771</v>
       </c>
       <c r="G191" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H191" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I191" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.35">
@@ -6541,10 +6552,10 @@
         <v>5231243349</v>
       </c>
       <c r="B192" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C192" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D192">
         <v>2025</v>
@@ -6556,13 +6567,13 @@
         <v>-118.9731</v>
       </c>
       <c r="G192" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H192" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I192" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.35">
@@ -6570,10 +6581,10 @@
         <v>5231315307</v>
       </c>
       <c r="B193" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D193">
         <v>2025</v>
@@ -6585,13 +6596,13 @@
         <v>-119.0252</v>
       </c>
       <c r="G193" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H193" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I193" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.35">
@@ -6599,10 +6610,10 @@
         <v>5231326322</v>
       </c>
       <c r="B194" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C194" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D194">
         <v>2025</v>
@@ -6614,13 +6625,13 @@
         <v>-119.0474</v>
       </c>
       <c r="G194" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H194" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I194" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.35">
@@ -6628,10 +6639,10 @@
         <v>5231338281</v>
       </c>
       <c r="B195" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C195" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D195">
         <v>2025</v>
@@ -6643,13 +6654,13 @@
         <v>-118.5968</v>
       </c>
       <c r="G195" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H195" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I195" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.35">
@@ -6657,10 +6668,10 @@
         <v>5231351292</v>
       </c>
       <c r="B196" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C196" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D196">
         <v>2025</v>
@@ -6672,13 +6683,13 @@
         <v>-119.0016</v>
       </c>
       <c r="G196" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H196" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I196" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.35">
@@ -6686,10 +6697,10 @@
         <v>5231384994</v>
       </c>
       <c r="B197" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C197" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D197">
         <v>2025</v>
@@ -6701,13 +6712,13 @@
         <v>-118.19750000000001</v>
       </c>
       <c r="G197" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H197" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I197" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.35">
@@ -6715,10 +6726,10 @@
         <v>5231400343</v>
       </c>
       <c r="B198" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D198">
         <v>2025</v>
@@ -6730,13 +6741,13 @@
         <v>-118.8506</v>
       </c>
       <c r="G198" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H198" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I198" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.35">
@@ -6744,10 +6755,10 @@
         <v>5231416332</v>
       </c>
       <c r="B199" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D199">
         <v>2025</v>
@@ -6759,13 +6770,13 @@
         <v>-118.98099999999999</v>
       </c>
       <c r="G199" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H199" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I199" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.35">
@@ -6773,10 +6784,10 @@
         <v>5231428072</v>
       </c>
       <c r="B200" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D200">
         <v>2025</v>
@@ -6788,13 +6799,13 @@
         <v>-117.27670000000001</v>
       </c>
       <c r="G200" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H200" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I200" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.35">
@@ -6802,10 +6813,10 @@
         <v>5231503243</v>
       </c>
       <c r="B201" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D201">
         <v>2025</v>
@@ -6817,13 +6828,13 @@
         <v>-118.5047</v>
       </c>
       <c r="G201" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H201" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I201" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
